--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.03903093849923</v>
+        <v>3.256342527506125</v>
       </c>
       <c r="D2" t="n">
-        <v>19.95188904693963</v>
+        <v>3.24218197012769</v>
       </c>
       <c r="E2" t="n">
-        <v>7.973634918042292</v>
+        <v>1.295715674181872</v>
       </c>
       <c r="F2" t="n">
-        <v>7.967495681876716</v>
+        <v>1.294718048304966</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.31053574600176</v>
+        <v>1.837962058725286</v>
       </c>
       <c r="D3" t="n">
-        <v>11.24619030715085</v>
+        <v>1.827505924912013</v>
       </c>
       <c r="E3" t="n">
-        <v>7.973634918042292</v>
+        <v>1.295715674181872</v>
       </c>
       <c r="F3" t="n">
-        <v>7.967495681876716</v>
+        <v>1.294718048304966</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.96281915655244</v>
+        <v>6.006458112939772</v>
       </c>
       <c r="D4" t="n">
-        <v>36.93943157302601</v>
+        <v>6.002657630616727</v>
       </c>
       <c r="E4" t="n">
-        <v>7.973634918042292</v>
+        <v>1.295715674181872</v>
       </c>
       <c r="F4" t="n">
-        <v>7.967495681876716</v>
+        <v>1.294718048304966</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.82275456861518</v>
+        <v>4.358697617399967</v>
       </c>
       <c r="D5" t="n">
-        <v>26.84107025179902</v>
+        <v>4.361673915917342</v>
       </c>
       <c r="E5" t="n">
-        <v>7.973634918042292</v>
+        <v>1.295715674181872</v>
       </c>
       <c r="F5" t="n">
-        <v>7.967495681876716</v>
+        <v>1.294718048304966</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.56317364526017</v>
+        <v>2.529015717354778</v>
       </c>
       <c r="D6" t="n">
-        <v>15.38245897139755</v>
+        <v>2.499649582852102</v>
       </c>
       <c r="E6" t="n">
-        <v>7.973634918042292</v>
+        <v>1.295715674181872</v>
       </c>
       <c r="F6" t="n">
-        <v>7.967495681876716</v>
+        <v>1.294718048304966</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.07064576827978</v>
+        <v>4.561479937345464</v>
       </c>
       <c r="D7" t="n">
-        <v>27.71421815319351</v>
+        <v>4.503560449893946</v>
       </c>
       <c r="E7" t="n">
-        <v>7.973634918042292</v>
+        <v>1.295715674181872</v>
       </c>
       <c r="F7" t="n">
-        <v>7.967495681876716</v>
+        <v>1.294718048304966</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.39506617987069</v>
+        <v>4.289198254228987</v>
       </c>
       <c r="D8" t="n">
-        <v>25.99268096670429</v>
+        <v>4.223810657089447</v>
       </c>
       <c r="E8" t="n">
-        <v>7.973634918042292</v>
+        <v>1.295715674181872</v>
       </c>
       <c r="F8" t="n">
-        <v>7.967495681876716</v>
+        <v>1.294718048304966</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
